--- a/TrackGestora_v2.xlsx
+++ b/TrackGestora_v2.xlsx
@@ -7085,36 +7085,120 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="A5" s="27" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Deploy</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Controllo regressioni sui 4 commit del 02/10: codice dell'app invariato, 292 test BE e 64 FE verdi, build come nel Dockerfile riuscita</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Al prossimo merge dev → main aprire Actions: job «test» verde con 292 test, poi «build-and-push» verde, poi /health su Azure</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Il workflow docker-publish è cambiato (test dalla radice) ma non è mai girato: parte solo su main</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="A6" s="27" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>.gitignore in radice sporco: blocco ripetuto due volte e una riga di testo finita per errore («- toglie il doppione di .vs/ e la riga di GestoraDocs.»)</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Togliere il blocco doppio e la riga sbagliata, poi commit «chore: .gitignore senza righe doppie»</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Non rompe niente. File delicato (regola 3): lo modifica Fabio o autorizza Claude</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n"/>
-      <c r="B7" s="24" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="A7" s="27" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Test spostati in GestoraWebApi.Tests/ e soluzione Gestora.sln in radice</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Aprire Gestora.sln in Visual Studio, Esplora test: devono risultare 292 test verdi</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n"/>
-      <c r="B8" s="24" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="A8" s="27" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Deploy</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Stato della CI non controllabile da Claude (gh non installato)</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Controllare su GitHub che CI Backend e CI Frontend siano verdi sull'ultimo commit di dev</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Dopo il push del riordino Fabio ha visto la CI verde</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="n"/>
@@ -10242,7 +10326,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="B5:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valore non previsto" error="Scegli un valore dall'elenco." type="list">
-      <formula1>"BE,FE,Database,Deploy,Documenti"</formula1>
+      <formula1>"BE,FE,Database,Deploy,Repository,Documenti"</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valore non previsto" error="Scegli un valore dall'elenco." type="list">
       <formula1>"Fatto,In corso,Da fare,Sospeso"</formula1>
